--- a/Packages/cn.etetet.yiuilubangen/Assets/Editor/Luban/Datas/Puzzle.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Assets/Editor/Luban/Datas/Puzzle.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unityproject\Game\Develop\Packages\cn.etetet.yiuilubangen\Assets\Editor\Luban\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56868C12-1FB4-4806-8CF5-AFC5EFB5BD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3844ADA3-A02C-41A3-9FA1-F269BDCDADA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2964" yWindow="4236" windowWidth="27900" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,38 @@
   </si>
   <si>
     <t>Puzzle/Puzzle1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SlotOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偏移量数组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三格拼图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Puzzle/Puzzle1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=;),(list#sep=,),int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -151,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -159,6 +191,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,10 +475,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="17.77734375" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,11 +501,11 @@
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -480,16 +519,16 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -499,10 +538,8 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -521,11 +558,11 @@
       <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -541,39 +578,45 @@
       <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
